--- a/docs/用于AI核销测试-费用分类及申请核销资料表.xlsx
+++ b/docs/用于AI核销测试-费用分类及申请核销资料表.xlsx
@@ -3,13 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\1、工作\1、各申请板块-填写模板\4、市场费用&amp;结算单-填写模板\厦门参半结算单模版\2026_08_21_附件：费用分类及申请核销资料表-2026.05.20版\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1356,7 +1351,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1393,14 +1388,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1816,7 +1814,7 @@
       </c>
     </row>
     <row r="5" ht="36" spans="1:7">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="12" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="9" t="s">
@@ -1839,7 +1837,7 @@
       </c>
     </row>
     <row r="6" ht="18" spans="1:7">
-      <c r="A6" s="11"/>
+      <c r="A6" s="13"/>
       <c r="B6" s="9" t="s">
         <v>23</v>
       </c>
@@ -1852,7 +1850,7 @@
       <c r="G6" s="10"/>
     </row>
     <row r="7" ht="18" spans="1:7">
-      <c r="A7" s="11"/>
+      <c r="A7" s="13"/>
       <c r="B7" s="9" t="s">
         <v>25</v>
       </c>
@@ -1865,7 +1863,7 @@
       <c r="G7" s="10"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="11"/>
+      <c r="A8" s="13"/>
       <c r="B8" s="9" t="s">
         <v>27</v>
       </c>
@@ -1878,7 +1876,7 @@
       <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B9" s="9" t="s">
@@ -1897,7 +1895,7 @@
       <c r="G9" s="10"/>
     </row>
     <row r="10" ht="27" spans="1:7">
-      <c r="A10" s="11"/>
+      <c r="A10" s="13"/>
       <c r="B10" s="9" t="s">
         <v>34</v>
       </c>
@@ -1910,7 +1908,7 @@
       <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="11"/>
+      <c r="A11" s="13"/>
       <c r="B11" s="9" t="s">
         <v>36</v>
       </c>
@@ -1923,7 +1921,7 @@
       <c r="G11" s="10"/>
     </row>
     <row r="12" ht="18" spans="1:7">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="12" t="s">
         <v>38</v>
       </c>
       <c r="B12" s="9" t="s">
@@ -1936,13 +1934,13 @@
       <c r="E12" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="12"/>
-      <c r="G12" s="13" t="s">
+      <c r="F12" s="14"/>
+      <c r="G12" s="15" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="11"/>
+      <c r="A13" s="13"/>
       <c r="B13" s="9" t="s">
         <v>43</v>
       </c>
@@ -1951,8 +1949,8 @@
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="13"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="15"/>
     </row>
     <row r="14" ht="18" spans="1:7">
       <c r="A14" s="6" t="s">
@@ -1966,8 +1964,8 @@
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="13"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="15"/>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" s="11"/>
@@ -1979,11 +1977,11 @@
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="13"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="15"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="90" spans="1:7">
-      <c r="A16" s="14"/>
+      <c r="A16" s="13"/>
       <c r="B16" s="9" t="s">
         <v>50</v>
       </c>
@@ -1997,7 +1995,7 @@
       <c r="F16" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="16" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2016,7 +2014,7 @@
         <v>58</v>
       </c>
       <c r="F17" s="4"/>
-      <c r="G17" s="15" t="s">
+      <c r="G17" s="16" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2031,7 +2029,7 @@
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
-      <c r="G18" s="15"/>
+      <c r="G18" s="16"/>
     </row>
     <row r="19" ht="72" spans="1:7">
       <c r="A19" s="6" t="s">
@@ -2048,7 +2046,7 @@
         <v>65</v>
       </c>
       <c r="F19" s="4"/>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="16" t="s">
         <v>66</v>
       </c>
     </row>
@@ -2067,7 +2065,7 @@
         <v>70</v>
       </c>
       <c r="F20" s="4"/>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="16" t="s">
         <v>71</v>
       </c>
     </row>
@@ -2086,7 +2084,7 @@
         <v>75</v>
       </c>
       <c r="F21" s="4"/>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="16" t="s">
         <v>76</v>
       </c>
     </row>
@@ -2101,7 +2099,7 @@
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
-      <c r="G22" s="15"/>
+      <c r="G22" s="16"/>
     </row>
     <row r="23" ht="45" spans="1:7">
       <c r="A23" s="6" t="s">
@@ -2118,7 +2116,7 @@
         <v>82</v>
       </c>
       <c r="F23" s="4"/>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="16" t="s">
         <v>83</v>
       </c>
     </row>
@@ -2138,8 +2136,8 @@
       <c r="E24" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="F24" s="12"/>
-      <c r="G24" s="15" t="s">
+      <c r="F24" s="14"/>
+      <c r="G24" s="16" t="s">
         <v>89</v>
       </c>
     </row>

--- a/docs/用于AI核销测试-费用分类及申请核销资料表.xlsx
+++ b/docs/用于AI核销测试-费用分类及申请核销资料表.xlsx
@@ -530,11 +530,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="6"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t xml:space="preserve">（1） 提供经销商盖章的 POS 数据，POS数据电子表；
 （2） </t>
     </r>
@@ -2000,7 +1995,7 @@
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:7">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="12" t="s">
         <v>55</v>
       </c>
       <c r="B17" s="9" t="s">
@@ -2019,7 +2014,7 @@
       </c>
     </row>
     <row r="18" ht="82" customHeight="1" spans="1:7">
-      <c r="A18" s="11"/>
+      <c r="A18" s="13"/>
       <c r="B18" s="9" t="s">
         <v>60</v>
       </c>
@@ -2051,7 +2046,7 @@
       </c>
     </row>
     <row r="20" ht="90" spans="1:7">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="12" t="s">
         <v>67</v>
       </c>
       <c r="B20" s="9" t="s">
